--- a/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市蓬江区建设三路商圈</t>
+          <t>-小米汽车广东省江门市蓬江区汇悦大融城</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>建设三路70号</t>
+          <t>白石大道166号汇悦・大融城1楼</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>-小米汽车广东省江门市蓬江区汇悦大融城</t>
+          <t>小米汽车广东省江门市蓬江区建设三路商圈</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>白石大道166号汇悦・大融城1楼</t>
+          <t>建设三路70号</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区武汉经开永旺</t>
+          <t>小米汽车湖北武汉市青山区滨江数字城授权服务中心</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>经开永旺梦乐城B馆一楼中央广场</t>
+          <t>滨江数字城28幢</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北武汉市青山区滨江数字城授权服务中心</t>
+          <t>小米汽车湖北省武汉市汉阳区武汉经开永旺</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>滨江数字城28幢</t>
+          <t>经开永旺梦乐城B馆一楼中央广场</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>台州中升睿迪汽车销售服务有限公司</t>
+          <t>台州中升悦迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市黄岩区北城街道二环北路 171 号</t>
+          <t>浙江省台州市玉环市玉环经济开发区银湖大道 55 号 AB7 号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>台州中升悦迪汽车销售服务有限公司</t>
+          <t>台州中升睿迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市玉环市玉环经济开发区银湖大道 55 号 AB7 号</t>
+          <t>浙江省台州市黄岩区北城街道二环北路 171 号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -12581,22 +12581,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
+          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
+          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
+          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米 → 安徽省六安市裕安区梅花路与磨子潭路交叉口</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
+          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
         </is>
       </c>
     </row>
@@ -12714,17 +12714,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12734,14 +12734,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米 → 安徽省六安市裕安区梅花路与磨子潭路交叉口</t>
+          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
+          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
         </is>
       </c>
     </row>
@@ -12783,12 +12783,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>长江西路1001号 → 长江西路1001号40幢</t>
+          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12862,29 +12862,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
+          <t>长江西路1001号 → 长江西路1001号40幢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12926,29 +12926,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
+          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12958,29 +12958,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
+          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12990,14 +12990,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
+          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13007,12 +13007,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13022,29 +13022,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
+          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13054,29 +13054,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
+          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13086,29 +13086,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
+          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
+          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
         </is>
       </c>
     </row>
@@ -13157,22 +13157,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 咸阳秦都</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 咸阳秦都</t>
+          <t>小米汽车上海市闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13221,22 +13221,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 湖州长兴汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 湖州长兴汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13285,22 +13285,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德体验店</t>
+          <t>蔚来空间 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德特斯拉中心</t>
+          <t>蔚来体验中心 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13349,22 +13349,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>佛山顺德体验店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城</t>
+          <t>佛山顺德特斯拉中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13386,17 +13386,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 抚州赣东汽车城</t>
+          <t>蔚来空间 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 抚州赣东汽车城</t>
+          <t>蔚来体验中心 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13413,22 +13413,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>蔚来空间 | 咸阳秦都</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
+          <t>蔚来体验中心 | 咸阳秦都</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
@@ -10142,7 +10142,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深圳宝安保时捷售后服务中心</t>
+          <t>深圳福田保时捷城市服务中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>宝安区福海街道桥头上社区富桥四区1栋101</t>
+          <t>广东省深圳市福田区侨城东路2006号</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>深圳福田保时捷城市服务中心</t>
+          <t>深圳宝安保时捷售后服务中心</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区侨城东路2006号</t>
+          <t>宝安区福海街道桥头上社区富桥四区1栋101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京亦庄龙湖</t>
+          <t>华为智能生活馆•北京中关村大融城</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
+          <t>北京市海淀区中关村大街15号中关村大融城东区1层、B1层 L1-01、L1-02、LG1-01、LG1-02号商铺</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京中关村大融城</t>
+          <t>华为智能生活馆•北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>北京市海淀区中关村大街15号中关村大融城东区1层、B1层 L1-01、L1-02、LG1-01、LG1-02号商铺</t>
+          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -12581,22 +12581,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
+          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米 → 安徽省六安市裕安区梅花路与磨子潭路交叉口</t>
+          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
+          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米 → 安徽省六安市裕安区梅花路与磨子潭路交叉口</t>
         </is>
       </c>
     </row>
@@ -12714,17 +12714,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12734,29 +12734,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
+          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
+          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
+          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
+          <t>长江西路1001号 → 长江西路1001号40幢</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
+          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>长江西路1001号 → 长江西路1001号40幢</t>
+          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12926,29 +12926,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12958,14 +12958,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
+          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12975,12 +12975,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12990,29 +12990,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
+          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13022,29 +13022,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
+          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13054,29 +13054,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
+          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
+          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
         </is>
       </c>
     </row>
@@ -13098,17 +13098,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
+          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
         </is>
       </c>
     </row>
@@ -13157,22 +13157,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>蔚来空间 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城</t>
+          <t>蔚来体验中心 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13221,22 +13221,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>佛山顺德体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
+          <t>佛山顺德特斯拉中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13253,22 +13253,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>蔚来空间 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>蔚来体验中心 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13285,22 +13285,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 抚州赣东汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 抚州赣东汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（大信新都汇广场）</t>
+          <t>蔚来空间 | 咸阳秦都</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（小榄大信新都汇）</t>
+          <t>蔚来体验中心 | 咸阳秦都</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13349,22 +13349,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德体验店</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德特斯拉中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13381,22 +13381,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 湖州长兴汽车城</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 湖州长兴汽车城</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13413,22 +13413,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 咸阳秦都</t>
+          <t>华为授权体验店（大信新都汇广场）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 咸阳秦都</t>
+          <t>华为授权体验店（小榄大信新都汇）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
@@ -10142,7 +10142,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深圳福田保时捷城市服务中心</t>
+          <t>深圳宝安保时捷售后服务中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区侨城东路2006号</t>
+          <t>宝安区福海街道桥头上社区富桥四区1栋101</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>深圳宝安保时捷售后服务中心</t>
+          <t>深圳福田保时捷城市服务中心</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>宝安区福海街道桥头上社区富桥四区1栋101</t>
+          <t>广东省深圳市福田区侨城东路2006号</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>台州中升悦迪汽车销售服务有限公司</t>
+          <t>台州中升睿迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市玉环市玉环经济开发区银湖大道 55 号 AB7 号</t>
+          <t>浙江省台州市黄岩区北城街道二环北路 171 号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>台州中升睿迪汽车销售服务有限公司</t>
+          <t>台州中升悦迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市黄岩区北城街道二环北路 171 号</t>
+          <t>浙江省台州市玉环市玉环经济开发区银湖大道 55 号 AB7 号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -12581,22 +12581,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12606,29 +12606,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
+          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
+          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
         </is>
       </c>
     </row>
@@ -12650,17 +12650,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
+          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安城南销售展厅</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米 → 安徽省六安市裕安区梅花路与磨子潭路交叉口</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12734,29 +12734,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
+          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
+          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
+          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>长江西路1001号 → 长江西路1001号40幢</t>
+          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车六安城南销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12862,29 +12862,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
+          <t>安徽省六安市裕安区梅花路与磨子潭路交叉口东南20米 → 安徽省六安市裕安区梅花路与磨子潭路交叉口</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
+          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12906,17 +12906,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12926,29 +12926,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
+          <t>长江西路1001号 → 长江西路1001号40幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12958,29 +12958,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12990,29 +12990,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
+          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13022,14 +13022,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
+          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13039,12 +13039,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13054,29 +13054,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
+          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13086,29 +13086,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
+          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
+          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
         </is>
       </c>
     </row>
@@ -13157,22 +13157,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 抚州赣东汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 抚州赣东汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13189,22 +13189,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆万州区永佳路授权服务中心</t>
+          <t>蔚来空间 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆万州区永佳路服务中心</t>
+          <t>蔚来体验中心 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13253,22 +13253,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 湖州长兴汽车城</t>
+          <t>华为授权体验店（大信新都汇广场）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 湖州长兴汽车城</t>
+          <t>华为授权体验店（小榄大信新都汇）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13285,22 +13285,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>蔚来空间 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
+          <t>蔚来体验中心 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 咸阳秦都</t>
+          <t>小米汽车重庆万州区永佳路授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 咸阳秦都</t>
+          <t>小米汽车重庆万州区永佳路服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13349,22 +13349,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13381,22 +13381,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车上海市闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13413,22 +13413,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（大信新都汇广场）</t>
+          <t>蔚来空间 | 咸阳秦都</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（小榄大信新都汇）</t>
+          <t>蔚来体验中心 | 咸阳秦都</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260803_vs_20260810.xlsx
@@ -10142,7 +10142,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深圳宝安保时捷售后服务中心</t>
+          <t>深圳福田保时捷城市服务中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>宝安区福海街道桥头上社区富桥四区1栋101</t>
+          <t>广东省深圳市福田区侨城东路2006号</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>深圳福田保时捷城市服务中心</t>
+          <t>深圳宝安保时捷售后服务中心</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区侨城东路2006号</t>
+          <t>宝安区福海街道桥头上社区富桥四区1栋101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>-小米汽车广东省江门市蓬江区汇悦大融城</t>
+          <t>小米汽车广东省江门市蓬江区建设三路商圈</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>白石大道166号汇悦・大融城1楼</t>
+          <t>建设三路70号</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市蓬江区建设三路商圈</t>
+          <t>-小米汽车广东省江门市蓬江区汇悦大融城</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>建设三路70号</t>
+          <t>白石大道166号汇悦・大融城1楼</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北武汉市青山区滨江数字城授权服务中心</t>
+          <t>小米汽车湖北省武汉市汉阳区武汉经开永旺</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>滨江数字城28幢</t>
+          <t>经开永旺梦乐城B馆一楼中央广场</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区武汉经开永旺</t>
+          <t>小米汽车湖北武汉市青山区滨江数字城授权服务中心</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>经开永旺梦乐城B馆一楼中央广场</t>
+          <t>滨江数字城28幢</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>台州中升睿迪汽车销售服务有限公司</t>
+          <t>台州中升悦迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市黄岩区北城街道二环北路 171 号</t>
+          <t>浙江省台州市玉环市玉环经济开发区银湖大道 55 号 AB7 号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>台州中升悦迪汽车销售服务有限公司</t>
+          <t>台州中升睿迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市玉环市玉环经济开发区银湖大道 55 号 AB7 号</t>
+          <t>浙江省台州市黄岩区北城街道二环北路 171 号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京中关村大融城</t>
+          <t>华为智能生活馆•北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>北京市海淀区中关村大街15号中关村大融城东区1层、B1层 L1-01、L1-02、LG1-01、LG1-02号商铺</t>
+          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京亦庄龙湖</t>
+          <t>华为智能生活馆•北京中关村大融城</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
+          <t>北京市海淀区中关村大街15号中关村大融城东区1层、B1层 L1-01、L1-02、LG1-01、LG1-02号商铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -12581,22 +12581,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>绵阳保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12606,14 +12606,14 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
+          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山万象汇</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12638,29 +12638,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
+          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>绵阳保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12670,29 +12670,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>绵阳高新区永兴镇辽宁大道西侧B-10号 → 绵阳市高新区永兴镇辽宁大道西侧B-10号</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁 → 星河WORLD·COCO Park购物中心</t>
+          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -12714,17 +12714,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
+          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12734,29 +12734,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
+          <t>长江西路1001号 → 长江西路1001号40幢</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省茂名市电白区水东万达</t>
+          <t>小鹏汽车昆明车行天下服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12766,29 +12766,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
+          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>珠海美东</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12798,29 +12798,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
+          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车浙江湖州市安吉县安吉浙北大厦</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市七星关区碧阳大道佰润汽车公园 → 贵州省毕节市碧阳大道佰润汽车公园</t>
+          <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心 → 浙江省湖州市安吉县昌硕街道云鸿东路1号安吉浙北购物中心</t>
         </is>
       </c>
     </row>
@@ -12869,22 +12869,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明车行天下服务中心</t>
+          <t>唐山保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12894,29 +12894,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区车行天下2期新东集A座B1层 → 云南省昆明市盘龙区车行天下2期新东集A座B1层小鹏汽车</t>
+          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市宝山区长江西路汽车园销售服务中心</t>
+          <t>小鹏汽车九江新港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12926,14 +12926,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>长江西路1001号 → 长江西路1001号40幢</t>
+          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>深圳罗湖万象城体验店</t>
+          <t>小米汽车广东省茂名市电白区水东万达</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12958,29 +12958,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
+          <t>广东省茂名市电白区水东街道迎宾大道中 66 号万达广场 1 楼 → 广东省茂名市电白区水东街道迎宾大道中66号万达广场1楼</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>唐山保时捷认可易手车及售后服务中心</t>
+          <t>小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12990,29 +12990,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省唐山市开平区高新技术产业开发区园区道911号 → 唐山市开平区高新技术产业开发区园区道911号</t>
+          <t>重庆市北碚区天生街道北碚吾悦广场1F1028号铺 → 小鹏汽车重庆北碚吾悦广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省烟台市福山区开发区万达</t>
+          <t>蔚来空间 | 杭州萧山万象汇</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13022,14 +13022,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
+          <t>浙江省杭州市萧山区北干街道金城路927号萧山万象汇L181 → 浙江省杭州市萧山区北干街道金城路927号杭州萧山万象汇L0185</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13039,12 +13039,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>珠海美东</t>
+          <t>深圳罗湖万象城体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>珠海市香洲区华宇路311号汽车展销中心A座101 → 珠海市香洲区前山梅溪工业区旅游路68号1栋</t>
+          <t>广东省深圳市罗湖区宝安南路1881号深圳万象城 → 广东省深圳市罗湖区桂园街道宝安南路1881号深圳万象城B1层B103</t>
         </is>
       </c>
     </row>
@@ -13066,17 +13066,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车九江新港汽车城销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13086,29 +13086,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江西省九江市濂溪区新港镇太平桥村13组新港汽车城东风日产旁 → 江西省九江市濂溪区九瑞大道270号</t>
+          <t>浙江省义乌市 北苑路 300 号 （十亿客创业园内） → 浙江省金华市义乌市北苑路300号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省烟台市福山区开发区万达</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>海宁大道9号 → 浙江省嘉兴市海宁市海宁大道9号</t>
+          <t>山东省烟台市福山区开发区万达广场1楼中庭 → 开发区万达广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13157,22 +13157,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>华为授权体验店（大信新都汇广场）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
+          <t>华为授权体验店（小榄大信新都汇）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13189,22 +13189,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 湖州长兴汽车城</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 湖州长兴汽车城</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13253,22 +13253,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（大信新都汇广场）</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（小榄大信新都汇）</t>
+          <t>小米汽车上海市闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13285,22 +13285,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 抚州赣东汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 抚州赣东汽车城</t>
+          <t>小米汽车福建省厦门市同安区同安爱琴海</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13349,22 +13349,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>蔚来空间 | 咸阳秦都</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>蔚来体验中心 | 咸阳秦都</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13381,22 +13381,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>蔚来空间 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城</t>
+          <t>蔚来体验中心 | 抚州赣东汽车城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13418,17 +13418,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 咸阳秦都</t>
+          <t>蔚来空间 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 咸阳秦都</t>
+          <t>蔚来体验中心 | 湖州长兴汽车城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13482,17 +13482,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路零售中心</t>
+          <t>小米汽车四川省成都市成华区成都万象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>小米之家四川省成都市成华区成都万象城汽车旗舰店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 78%</t>
         </is>
       </c>
     </row>
@@ -13514,17 +13514,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市成华区成都万象城</t>
+          <t>小米汽车江苏省南京市秦淮区大明路零售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家四川省成都市成华区成都万象城汽车旗舰店</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 78%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
